--- a/data/trending_integrated_20261013_14.xlsx
+++ b/data/trending_integrated_20261013_14.xlsx
@@ -584,7 +584,7 @@
         <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87693661290</v>
+        <v>87696593810</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4265</v>
+        <v>4250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.50%</t>
+          <t>'+9.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
         <v>152</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>100856932743</v>
+        <v>102207662593</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11990</v>
+        <v>11730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.31%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F4" t="n">
         <v>137</v>
       </c>
       <c r="G4" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>381418018750</v>
+        <v>383542303320</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>급등 후 급락 및 개인 투자자 털기 관점. 주포의 움직임과 함께 추세를 지켜봐야 함.</t>
+          <t>주포의 움직임을 주시하며 매도 성공. 호남클러스터 외 테마 소멸 우려 속 인생 역전 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '패턴', '물갈이']</t>
+          <t>['주포', '호남클러스터', '매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16840</v>
+        <v>16850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.00%</t>
+          <t>'+3.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G5" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
@@ -886,7 +886,7 @@
         <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>248283750010</v>
+        <v>248825294065</v>
       </c>
       <c r="P5" t="n">
         <v>19930</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 보안주 폭락에도 불구하고, 국내 보안주로서의 강세 및 신고가 돌파 기대감 형성. 사명 변경 이슈.</t>
+          <t>미국 보안주 폭락 속에서 상승 추세 기대. 보안 기술 중요성 부각 및 신고가 돌파 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', '사명변경']</t>
+          <t>['보안주', '신고가', '기술']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3785</v>
+        <v>3815</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.83%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F6" t="n">
         <v>70</v>
@@ -978,7 +978,7 @@
         <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>97284022169</v>
+        <v>97478357519</v>
       </c>
       <c r="P6" t="n">
         <v>6660</v>
@@ -1023,162 +1023,162 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17970</v>
+        <v>44500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="F7" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="G7" t="n">
-        <v>336</v>
+        <v>995</v>
       </c>
       <c r="H7" t="n">
-        <v>27.69</v>
+        <v>13.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18010</v>
+        <v>44400</v>
       </c>
       <c r="K7" t="n">
-        <v>17430</v>
+        <v>43300</v>
       </c>
       <c r="L7" t="n">
-        <v>18000</v>
+        <v>44800</v>
       </c>
       <c r="M7" t="n">
-        <v>17210</v>
+        <v>42250</v>
       </c>
       <c r="N7" t="n">
-        <v>27.61</v>
+        <v>13.33</v>
       </c>
       <c r="O7" t="n">
-        <v>62723311720</v>
+        <v>31233522525</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>17210</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>743000</v>
+        <v>70000</v>
       </c>
       <c r="S7" t="n">
-        <v>65000</v>
+        <v>12000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
+          <t>간암 1차 승인 시 200조 딜 기대감. C1 확정 및 AI 기반 90% 이상 승인 예측. 하반기 주도주 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 확대', '목표가']</t>
+          <t>['간암', '승인', 'AI']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1557</v>
+        <v>18040</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.33%</t>
+          <t>'+0.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="G8" t="n">
-        <v>244</v>
+        <v>342</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>27.69</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1578</v>
+        <v>18010</v>
       </c>
       <c r="K8" t="n">
-        <v>1578</v>
+        <v>17430</v>
       </c>
       <c r="L8" t="n">
-        <v>1776</v>
+        <v>18050</v>
       </c>
       <c r="M8" t="n">
-        <v>1457</v>
+        <v>17210</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>9212252719</v>
+        <v>63758060820</v>
       </c>
       <c r="P8" t="n">
-        <v>2930</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>910</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>53000</v>
+        <v>743000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
+          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
+          <t>['FLNG', '매출 확대', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15870</v>
+        <v>15930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.37%</t>
+          <t>'-0.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H9" t="n">
         <v>9.630000000000001</v>
@@ -1254,7 +1254,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>56698487180</v>
+        <v>57375206190</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1299,175 +1299,175 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69600</v>
+        <v>1551</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-1.71%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>241</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>757</v>
+        <v>245</v>
       </c>
       <c r="H10" t="n">
-        <v>22.1</v>
+        <v>0.32</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>71500</v>
+        <v>1578</v>
       </c>
       <c r="K10" t="n">
-        <v>68400</v>
+        <v>1578</v>
       </c>
       <c r="L10" t="n">
-        <v>70600</v>
+        <v>1776</v>
       </c>
       <c r="M10" t="n">
-        <v>67300</v>
+        <v>1457</v>
       </c>
       <c r="N10" t="n">
-        <v>22.21</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>161329005600</v>
+        <v>9223733347</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>85000</v>
+        <v>53000</v>
       </c>
       <c r="S10" t="n">
-        <v>-50000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주식 시장 전반에 대한 불만과 함께 특정 인물들에 대한 비판이 제기됨. 원전 사업 관련 불확실성과 반대매매 발생 가능성이 언급되며 주가 하락 우려가 있음.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '반대매매', '주가 하락']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44600</v>
+        <v>70000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>-0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="F11" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="G11" t="n">
-        <v>918</v>
+        <v>759</v>
       </c>
       <c r="H11" t="n">
-        <v>13.1</v>
+        <v>22.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>46000</v>
+        <v>71500</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>68400</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>70600</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="N11" t="n">
-        <v>13.33</v>
+        <v>22.21</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>163643469800</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>70000</v>
+        <v>85000</v>
       </c>
       <c r="S11" t="n">
-        <v>12000</v>
+        <v>-50000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>간암 1차 승인 기대감과 함께 매수 시점이 다가왔다는 의견이 있음. 악성 매물대 소화 및 통합 IR 데이 관련 언급이 있으며, AI 분석에서 긍정적인 전망을 제시함.</t>
+          <t>주식 시장 전반에 대한 불만과 함께 특정 인물들에 대한 비판이 제기됨. 원전 사업 관련 불확실성과 반대매매 발생 가능성이 언급되며 주가 하락 우려가 있음.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['간암 1차 승인', 'IR 데이', '매물대']</t>
+          <t>['원전', '반대매매', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17980</v>
+        <v>6020</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.07%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.42</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="H12" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18550</v>
+        <v>6210</v>
       </c>
       <c r="K12" t="n">
-        <v>17550</v>
+        <v>5950</v>
       </c>
       <c r="L12" t="n">
-        <v>19580</v>
+        <v>6560</v>
       </c>
       <c r="M12" t="n">
-        <v>17010</v>
+        <v>5840</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>73728532715</v>
+        <v>23573483675</v>
       </c>
       <c r="P12" t="n">
-        <v>30550</v>
+        <v>11370</v>
       </c>
       <c r="Q12" t="n">
-        <v>6100</v>
+        <v>3300</v>
       </c>
       <c r="R12" t="n">
-        <v>-36000</v>
+        <v>78000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6000</v>
+        <v>17960</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>-0.42</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6210</v>
+        <v>18550</v>
       </c>
       <c r="K13" t="n">
-        <v>5950</v>
+        <v>17550</v>
       </c>
       <c r="L13" t="n">
-        <v>6560</v>
+        <v>19580</v>
       </c>
       <c r="M13" t="n">
-        <v>5840</v>
+        <v>17010</v>
       </c>
       <c r="N13" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="O13" t="n">
-        <v>23434798725</v>
+        <v>73830165275</v>
       </c>
       <c r="P13" t="n">
-        <v>11370</v>
+        <v>30550</v>
       </c>
       <c r="Q13" t="n">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="R13" t="n">
-        <v>78000</v>
+        <v>-36000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7470</v>
+        <v>7490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.74%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" t="n">
         <v>439</v>
@@ -1714,7 +1714,7 @@
         <v>26.37</v>
       </c>
       <c r="O14" t="n">
-        <v>24810812415</v>
+        <v>25163071705</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1777,10 +1777,10 @@
         <v>162</v>
       </c>
       <c r="F15" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" t="n">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H15" t="n">
         <v>12.27</v>
@@ -1806,7 +1806,7 @@
         <v>12.57</v>
       </c>
       <c r="O15" t="n">
-        <v>20657233585</v>
+        <v>20993598535</v>
       </c>
       <c r="P15" t="n">
         <v>8850</v>
@@ -1855,18 +1855,18 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12820</v>
+        <v>12870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.40%</t>
+          <t>'-4.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F16" t="n">
         <v>93</v>
@@ -1898,7 +1898,7 @@
         <v>0.21</v>
       </c>
       <c r="O16" t="n">
-        <v>66873791335</v>
+        <v>67044132225</v>
       </c>
       <c r="P16" t="n">
         <v>28700</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19500</v>
+        <v>19320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-5.53%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.39</v>
       </c>
       <c r="E17" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F17" t="n">
         <v>126</v>
       </c>
       <c r="G17" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="H17" t="n">
         <v>0.73</v>
@@ -1990,7 +1990,7 @@
         <v>0.34</v>
       </c>
       <c r="O17" t="n">
-        <v>92425221840</v>
+        <v>93298817060</v>
       </c>
       <c r="P17" t="n">
         <v>62100</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>보호예수, 물량 떠넘기기, 주가 조작 의혹 등 부정적인 내용이 지배적임. 단기 급등 후 급락하는 패턴이 반복되며 투자자들의 손실이 언급됨.</t>
+          <t>주가 조작 의혹 및 반복적인 상승 후 하락 패턴 지적. 코인 시장과 유사한 움직임에 대한 불신.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 조작', '보호예수', '단기 급등']</t>
+          <t>['주가조작', '먹튀', '코인']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>175100</v>
+        <v>176000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.26%</t>
+          <t>'-5.78%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
         <v>169</v>
@@ -2082,7 +2082,7 @@
         <v>75.23</v>
       </c>
       <c r="O18" t="n">
-        <v>648786141600</v>
+        <v>660715444250</v>
       </c>
       <c r="P18" t="n">
         <v>243500</v>
@@ -2127,79 +2127,79 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14530</v>
+        <v>233250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.57%</t>
+          <t>'-6.89%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E19" t="n">
-        <v>119</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>77</v>
+        <v>557</v>
       </c>
       <c r="G19" t="n">
-        <v>407</v>
+        <v>1735</v>
       </c>
       <c r="H19" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K19" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L19" t="n">
-        <v>15130</v>
+        <v>244000</v>
       </c>
       <c r="M19" t="n">
-        <v>14160</v>
+        <v>228000</v>
       </c>
       <c r="N19" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O19" t="n">
-        <v>80318976555</v>
+        <v>4290372408500</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R19" t="n">
-        <v>79000</v>
+        <v>-4524000</v>
       </c>
       <c r="S19" t="n">
-        <v>-7000</v>
+        <v>383000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 근거 기반으로 주가 급등 전망. 미국 업체 기술력 하락 언급.</t>
+          <t>대통령 선출 실패 및 정치적 이슈로 인한 증시 전반의 하락세 분석. 기술 유출 처벌 및 재총선 요구.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '외인매수', '공장']</t>
+          <t>['대통령', '정치', '기술유출']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,91 +2207,91 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>231250</v>
+        <v>14630</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.68%</t>
+          <t>'-6.93%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>121</v>
       </c>
       <c r="F20" t="n">
-        <v>558</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>1737</v>
+        <v>409</v>
       </c>
       <c r="H20" t="n">
-        <v>46.3</v>
+        <v>3.43</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>250500</v>
+        <v>15720</v>
       </c>
       <c r="K20" t="n">
-        <v>241500</v>
+        <v>14770</v>
       </c>
       <c r="L20" t="n">
-        <v>244000</v>
+        <v>15130</v>
       </c>
       <c r="M20" t="n">
-        <v>228000</v>
+        <v>14160</v>
       </c>
       <c r="N20" t="n">
-        <v>46.35</v>
+        <v>3.37</v>
       </c>
       <c r="O20" t="n">
-        <v>4187681232750</v>
+        <v>81052769205</v>
       </c>
       <c r="P20" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>-4524000</v>
+        <v>79000</v>
       </c>
       <c r="S20" t="n">
-        <v>383000</v>
+        <v>-7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 삼성전자 주가 하락에 대한 불만 토로. 외인 매수 기대는 있으나, 근거 부족.</t>
+          <t>3분기 어닝 서프라이즈 기록 및 외인 대량 매수에도 불구하고 주가 하락. 미국 AI 거품론 영향.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '이재명']</t>
+          <t>['어닝서프라이즈', '외인매수', 'AI거품론']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12360</v>
+        <v>12250</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.76%</t>
+          <t>'-8.58%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>194642496600</v>
+        <v>195116910960</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1454000</v>
+        <v>1467000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.41%</t>
+          <t>'-8.60%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="G22" t="n">
-        <v>1444</v>
+        <v>1420</v>
       </c>
       <c r="H22" t="n">
         <v>49.41</v>
@@ -2450,7 +2450,7 @@
         <v>49.52</v>
       </c>
       <c r="O22" t="n">
-        <v>5687416865000</v>
+        <v>5772958091000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 반도체 산업 악화 우려. 외국인 투자자 이탈 및 주가 하락 전망.</t>
+          <t>중국 반도체 투자 및 국내 정치 이슈로 인한 주가 하락 우려. 부동산 투자 선호 현상.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '정치', '외국인']</t>
+          <t>['반도체', '정치', '부동산']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6640</v>
+        <v>6670</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.39%</t>
+          <t>'-9.99%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.19</v>
       </c>
       <c r="E23" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F23" t="n">
         <v>65</v>
       </c>
       <c r="G23" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H23" t="n">
         <v>1.8</v>
@@ -2542,7 +2542,7 @@
         <v>1.99</v>
       </c>
       <c r="O23" t="n">
-        <v>68808031065</v>
+        <v>69056402910</v>
       </c>
       <c r="P23" t="n">
         <v>23500</v>

--- a/data/trending_integrated_20261013_14.xlsx
+++ b/data/trending_integrated_20261013_14.xlsx
@@ -584,7 +584,7 @@
         <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87696593810</v>
+        <v>87715901030</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 확대 추진 수혜주로 부각되며 급등. 투자 주의 종목 지정에도 불구하고 연상 랠리 지속 전망.</t>
+          <t>대규모 호재성 뉴스 및 투자 주의에도 불구하고 급등세 지속, 수혜주 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['수혜주', '반도체', '투자주의']</t>
+          <t>['호재', '수혜주', '투자주의']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4250</v>
+        <v>4390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.11%</t>
+          <t>'+12.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>102207662593</v>
+        <v>105261739258</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11730</v>
+        <v>11740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+6.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G4" t="n">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>383542303320</v>
+        <v>386477114665</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주포의 움직임을 주시하며 매도 성공. 호남클러스터 외 테마 소멸 우려 속 인생 역전 기대.</t>
+          <t>급등락 반복, 주포 활동 의심 및 향후 상승 기대 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '호남클러스터', '매도']</t>
+          <t>['주포', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16850</v>
+        <v>16960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.06%</t>
+          <t>'+3.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
@@ -886,7 +886,7 @@
         <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>248825294065</v>
+        <v>250187255735</v>
       </c>
       <c r="P5" t="n">
         <v>19930</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 보안주 폭락 속에서 상승 추세 기대. 보안 기술 중요성 부각 및 신고가 돌파 가능성.</t>
+          <t>보안주 테마 상승 기대 및 신고가 돌파 가능성 언급, 국제 정세 불안 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', '기술']</t>
+          <t>['보안주', '신고가', '국제정세']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3815</v>
+        <v>18180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>146</v>
+        <v>351</v>
       </c>
       <c r="H6" t="n">
-        <v>0.91</v>
+        <v>27.69</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3710</v>
+        <v>18010</v>
       </c>
       <c r="K6" t="n">
-        <v>3555</v>
+        <v>17430</v>
       </c>
       <c r="L6" t="n">
-        <v>4440</v>
+        <v>18190</v>
       </c>
       <c r="M6" t="n">
-        <v>3475</v>
+        <v>17210</v>
       </c>
       <c r="N6" t="n">
-        <v>0.78</v>
+        <v>27.61</v>
       </c>
       <c r="O6" t="n">
-        <v>97478357519</v>
+        <v>66152226765</v>
       </c>
       <c r="P6" t="n">
-        <v>6660</v>
+        <v>35350</v>
       </c>
       <c r="Q6" t="n">
-        <v>2200</v>
+        <v>17210</v>
       </c>
       <c r="R6" t="n">
-        <v>-120000</v>
+        <v>743000</v>
       </c>
       <c r="S6" t="n">
-        <v>-18000</v>
+        <v>65000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>러시아발 페스트 관련주로 부각되며 상승 기대감 형성. 다만, 관련 뉴스 신뢰도 및 백신 개발 여부 불확실.</t>
+          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['페스트', '러시아', '백신']</t>
+          <t>['FLNG', '매출 확대', '목표가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44500</v>
+        <v>3735</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.23</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>995</v>
+        <v>146</v>
       </c>
       <c r="H7" t="n">
-        <v>13.1</v>
+        <v>0.91</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>44400</v>
+        <v>3710</v>
       </c>
       <c r="K7" t="n">
-        <v>43300</v>
+        <v>3555</v>
       </c>
       <c r="L7" t="n">
-        <v>44800</v>
+        <v>4440</v>
       </c>
       <c r="M7" t="n">
-        <v>42250</v>
+        <v>3475</v>
       </c>
       <c r="N7" t="n">
-        <v>13.33</v>
+        <v>0.78</v>
       </c>
       <c r="O7" t="n">
-        <v>31233522525</v>
+        <v>98406340445</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>6660</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>2200</v>
       </c>
       <c r="R7" t="n">
-        <v>70000</v>
+        <v>-120000</v>
       </c>
       <c r="S7" t="n">
-        <v>12000</v>
+        <v>-18000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>간암 1차 승인 시 200조 딜 기대감. C1 확정 및 AI 기반 90% 이상 승인 예측. 하반기 주도주 전망.</t>
+          <t>러시아발 페스트 관련주로 부각되며 상승 기대감 형성. 다만, 관련 뉴스 신뢰도 및 백신 개발 여부 불확실.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['간암', '승인', 'AI']</t>
+          <t>['페스트', '러시아', '백신']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,99 +1108,99 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18040</v>
+        <v>44600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.17%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>234</v>
       </c>
       <c r="F8" t="n">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="G8" t="n">
-        <v>342</v>
+        <v>1063</v>
       </c>
       <c r="H8" t="n">
-        <v>27.69</v>
+        <v>13.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18010</v>
+        <v>44400</v>
       </c>
       <c r="K8" t="n">
-        <v>17430</v>
+        <v>43300</v>
       </c>
       <c r="L8" t="n">
-        <v>18050</v>
+        <v>44850</v>
       </c>
       <c r="M8" t="n">
-        <v>17210</v>
+        <v>42250</v>
       </c>
       <c r="N8" t="n">
-        <v>27.61</v>
+        <v>13.33</v>
       </c>
       <c r="O8" t="n">
-        <v>63758060820</v>
+        <v>32079987100</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>743000</v>
+        <v>70000</v>
       </c>
       <c r="S8" t="n">
-        <v>65000</v>
+        <v>12000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
+          <t>간암 1차 승인 기대감으로 인한 주가 상승 전망. 공매도 세력의 움직임 및 AI 분석 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 확대', '목표가']</t>
+          <t>['리보', '캄렐', '승인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15930</v>
+        <v>16030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.99%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="H9" t="n">
         <v>9.630000000000001</v>
@@ -1245,7 +1245,7 @@
         <v>15190</v>
       </c>
       <c r="L9" t="n">
-        <v>15980</v>
+        <v>16050</v>
       </c>
       <c r="M9" t="n">
         <v>15100</v>
@@ -1254,7 +1254,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>57375206190</v>
+        <v>59700485815</v>
       </c>
       <c r="P9" t="n">
         <v>40350</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 하락 및 공매도 세력에 대한 불만 표출. 수주 및 공시 기반의 긍정적 전망은 낮음.</t>
+          <t>금감원 사모펀드 점검 및 공매도 관련 언급, 지수 폭락에도 주가 방어력 요구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '주가', '수주']</t>
+          <t>['금감원', '공매도', '사모펀드']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,307 +1299,307 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1551</v>
+        <v>6570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.71%</t>
+          <t>'-1.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>245</v>
+        <v>681</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32</v>
+        <v>12.27</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1578</v>
+        <v>6640</v>
       </c>
       <c r="K10" t="n">
-        <v>1578</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1776</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1457</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>12.57</v>
       </c>
       <c r="O10" t="n">
-        <v>9223733347</v>
+        <v>21239000000</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>53000</v>
+        <v>-514000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
+          <t>공매도 세력의 주가 누르기 시도에도 불구하고, 금호타이어의 실적 개선 및 부지 개발 이슈로 인한 반등 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
+          <t>['공매도', '실적', '부지']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70000</v>
+        <v>1556</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-1.39%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>243</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>759</v>
+        <v>255</v>
       </c>
       <c r="H11" t="n">
-        <v>22.1</v>
+        <v>0.32</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71500</v>
+        <v>1578</v>
       </c>
       <c r="K11" t="n">
-        <v>68400</v>
+        <v>1578</v>
       </c>
       <c r="L11" t="n">
-        <v>70600</v>
+        <v>1776</v>
       </c>
       <c r="M11" t="n">
-        <v>67300</v>
+        <v>1457</v>
       </c>
       <c r="N11" t="n">
-        <v>22.21</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>163643469800</v>
+        <v>9260902413</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>85000</v>
+        <v>53000</v>
       </c>
       <c r="S11" t="n">
-        <v>-50000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주식 시장 전반에 대한 불만과 함께 특정 인물들에 대한 비판이 제기됨. 원전 사업 관련 불확실성과 반대매매 발생 가능성이 언급되며 주가 하락 우려가 있음.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '반대매매', '주가 하락']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6020</v>
+        <v>7520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-3.09%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="G12" t="n">
-        <v>129</v>
+        <v>447</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6899999999999999</v>
+        <v>26.01</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6210</v>
+        <v>7760</v>
       </c>
       <c r="K12" t="n">
-        <v>5950</v>
+        <v>7650</v>
       </c>
       <c r="L12" t="n">
-        <v>6560</v>
+        <v>7680</v>
       </c>
       <c r="M12" t="n">
-        <v>5840</v>
+        <v>7300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>26.37</v>
       </c>
       <c r="O12" t="n">
-        <v>23573483675</v>
+        <v>25753371260</v>
       </c>
       <c r="P12" t="n">
-        <v>11370</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>3300</v>
+        <v>7300</v>
       </c>
       <c r="R12" t="n">
-        <v>78000</v>
+        <v>-822000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>실적 부진 및 상장폐지 가능성 언급, 투자 확대 및 유상증자 예상.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['실적', '유상증자', '투자']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17960</v>
+        <v>6000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.42</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18550</v>
+        <v>6210</v>
       </c>
       <c r="K13" t="n">
-        <v>17550</v>
+        <v>5950</v>
       </c>
       <c r="L13" t="n">
-        <v>19580</v>
+        <v>6560</v>
       </c>
       <c r="M13" t="n">
-        <v>17010</v>
+        <v>5840</v>
       </c>
       <c r="N13" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="O13" t="n">
-        <v>73830165275</v>
+        <v>23763173415</v>
       </c>
       <c r="P13" t="n">
-        <v>30550</v>
+        <v>11370</v>
       </c>
       <c r="Q13" t="n">
-        <v>6100</v>
+        <v>3300</v>
       </c>
       <c r="R13" t="n">
-        <v>-36000</v>
+        <v>78000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,182 +1660,182 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7490</v>
+        <v>17870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.36</v>
+        <v>-0.42</v>
       </c>
       <c r="E14" t="n">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>439</v>
+        <v>96</v>
       </c>
       <c r="H14" t="n">
-        <v>26.01</v>
+        <v>0.46</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7760</v>
+        <v>18550</v>
       </c>
       <c r="K14" t="n">
-        <v>7650</v>
+        <v>17550</v>
       </c>
       <c r="L14" t="n">
-        <v>7680</v>
+        <v>19580</v>
       </c>
       <c r="M14" t="n">
-        <v>7300</v>
+        <v>17010</v>
       </c>
       <c r="N14" t="n">
-        <v>26.37</v>
+        <v>0.88</v>
       </c>
       <c r="O14" t="n">
-        <v>25163071705</v>
+        <v>74253082530</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>30550</v>
       </c>
       <c r="Q14" t="n">
-        <v>7300</v>
+        <v>6100</v>
       </c>
       <c r="R14" t="n">
-        <v>-822000</v>
+        <v>-36000</v>
       </c>
       <c r="S14" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 회사 경영진 교체 요구. 아이폰 패널 출하량 감소 등 부정적 뉴스 반영.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가', '패널', '아이폰']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6550</v>
+        <v>12720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.3</v>
+        <v>0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="F15" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G15" t="n">
-        <v>673</v>
+        <v>301</v>
       </c>
       <c r="H15" t="n">
-        <v>12.27</v>
+        <v>0.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6810</v>
+        <v>13410</v>
       </c>
       <c r="K15" t="n">
-        <v>7150</v>
+        <v>13260</v>
       </c>
       <c r="L15" t="n">
-        <v>7160</v>
+        <v>14580</v>
       </c>
       <c r="M15" t="n">
-        <v>6440</v>
+        <v>12680</v>
       </c>
       <c r="N15" t="n">
-        <v>12.57</v>
+        <v>0.21</v>
       </c>
       <c r="O15" t="n">
-        <v>20993598535</v>
+        <v>67487109150</v>
       </c>
       <c r="P15" t="n">
-        <v>8850</v>
+        <v>28700</v>
       </c>
       <c r="Q15" t="n">
-        <v>4220</v>
+        <v>11600</v>
       </c>
       <c r="R15" t="n">
-        <v>-514000</v>
+        <v>31000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 세력의 주가 누르기 시도에도 불구하고, 금호타이어의 실적 개선 및 부지 개발 이슈로 인한 반등 기대.</t>
+          <t>대차 잔고 및 공매도 관련 언급은 있으나, 투자자들은 명확한 분석 없이 주가 하락을 경험하고 있음. 매수세 유입 시 즉각적인 매도세가 나타나는 패턴이 관찰됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '실적', '부지']</t>
+          <t>['대차', '공매도', '매수세']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,99 +1844,99 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12870</v>
+        <v>176400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.03%</t>
+          <t>'-5.57%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>296</v>
+        <v>170</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13410</v>
+        <v>186800</v>
       </c>
       <c r="K16" t="n">
-        <v>13260</v>
+        <v>180800</v>
       </c>
       <c r="L16" t="n">
-        <v>14580</v>
+        <v>183000</v>
       </c>
       <c r="M16" t="n">
-        <v>12680</v>
+        <v>170000</v>
       </c>
       <c r="N16" t="n">
-        <v>0.21</v>
+        <v>75.23</v>
       </c>
       <c r="O16" t="n">
-        <v>67044132225</v>
+        <v>679131214950</v>
       </c>
       <c r="P16" t="n">
-        <v>28700</v>
+        <v>243500</v>
       </c>
       <c r="Q16" t="n">
-        <v>11600</v>
+        <v>70400</v>
       </c>
       <c r="R16" t="n">
-        <v>31000</v>
+        <v>-532000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>92000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대차 잔고 및 공매도 관련 언급은 있으나, 투자자들은 명확한 분석 없이 주가 하락을 경험하고 있음. 매수세 유입 시 즉각적인 매도세가 나타나는 패턴이 관찰됨.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차', '공매도', '매수세']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19320</v>
+        <v>19280</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.53%</t>
+          <t>'-5.72%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.39</v>
       </c>
       <c r="E17" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="F17" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G17" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H17" t="n">
         <v>0.73</v>
@@ -1990,7 +1990,7 @@
         <v>0.34</v>
       </c>
       <c r="O17" t="n">
-        <v>93298817060</v>
+        <v>95085698115</v>
       </c>
       <c r="P17" t="n">
         <v>62100</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 반복적인 상승 후 하락 패턴 지적. 코인 시장과 유사한 움직임에 대한 불신.</t>
+          <t>주가 조작 의심 및 단기 급등락 반복, 투자자 피해 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가조작', '먹튀', '코인']</t>
+          <t>['주가조작', '급등락', '투자자피해']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,92 +2035,92 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>176000</v>
+        <v>14710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.78%</t>
+          <t>'-6.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
-        <v>169</v>
+        <v>411</v>
       </c>
       <c r="H18" t="n">
-        <v>75.20999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>186800</v>
+        <v>15720</v>
       </c>
       <c r="K18" t="n">
-        <v>180800</v>
+        <v>14770</v>
       </c>
       <c r="L18" t="n">
-        <v>183000</v>
+        <v>15130</v>
       </c>
       <c r="M18" t="n">
-        <v>170000</v>
+        <v>14160</v>
       </c>
       <c r="N18" t="n">
-        <v>75.23</v>
+        <v>3.37</v>
       </c>
       <c r="O18" t="n">
-        <v>660715444250</v>
+        <v>82896653615</v>
       </c>
       <c r="P18" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>70400</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-532000</v>
+        <v>79000</v>
       </c>
       <c r="S18" t="n">
-        <v>92000</v>
+        <v>-7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>3분기 어닝 서프라이즈 기록 및 외인 대량 매수에도 불구하고 주가 하락. 미국 AI 거품론 영향.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['어닝서프라이즈', '외인매수', 'AI거품론']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="G19" t="n">
-        <v>1735</v>
+        <v>1711</v>
       </c>
       <c r="H19" t="n">
         <v>46.3</v>
@@ -2174,7 +2174,7 @@
         <v>46.35</v>
       </c>
       <c r="O19" t="n">
-        <v>4290372408500</v>
+        <v>4390999864500</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대통령 선출 실패 및 정치적 이슈로 인한 증시 전반의 하락세 분석. 기술 유출 처벌 및 재총선 요구.</t>
+          <t>정치적 이슈로 인한 급락 및 향후 반등 기대, 기술 유출 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['대통령', '정치', '기술유출']</t>
+          <t>['정치', '반도체', '기술유출']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,83 +2219,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14630</v>
+        <v>71100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.93%</t>
+          <t>'-7.30%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>121</v>
+        <v>249</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="G20" t="n">
-        <v>409</v>
+        <v>761</v>
       </c>
       <c r="H20" t="n">
-        <v>3.43</v>
+        <v>22.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15720</v>
+        <v>76700</v>
       </c>
       <c r="K20" t="n">
-        <v>14770</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>15130</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>14160</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.37</v>
+        <v>22.21</v>
       </c>
       <c r="O20" t="n">
-        <v>81052769205</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>79000</v>
+        <v>85000</v>
       </c>
       <c r="S20" t="n">
-        <v>-7000</v>
+        <v>-62000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록 및 외인 대량 매수에도 불구하고 주가 하락. 미국 AI 거품론 영향.</t>
+          <t>주식 시장 전반에 대한 불만과 함께 특정 인물들에 대한 비판이 제기됨. 원전 사업 관련 불확실성과 반대매매 발생 가능성이 언급되며 주가 하락 우려가 있음.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '외인매수', 'AI거품론']</t>
+          <t>['원전', '반대매매', '주가 하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12250</v>
+        <v>12310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.58%</t>
+          <t>'-8.13%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G21" t="n">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>195116910960</v>
+        <v>195940787740</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>단기 급등 후 하락에 대한 실망감 표출. 외인 매수세 약화 및 주가 하락 예상.</t>
+          <t>주포 활동 의심 및 목표가 제시, 경쟁사 상승 대비 주가 부진 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['외인', '주가', '반도체']</t>
+          <t>['주포', '목표가', '경쟁사']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1467000</v>
+        <v>1470000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.60%</t>
+          <t>'-8.41%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G22" t="n">
-        <v>1420</v>
+        <v>1430</v>
       </c>
       <c r="H22" t="n">
         <v>49.41</v>
@@ -2450,7 +2450,7 @@
         <v>49.52</v>
       </c>
       <c r="O22" t="n">
-        <v>5772958091000</v>
+        <v>5925178575000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>중국 반도체 투자 및 국내 정치 이슈로 인한 주가 하락 우려. 부동산 투자 선호 현상.</t>
+          <t>정치적 이슈 및 외부 요인으로 인한 주가 하락, 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '정치', '부동산']</t>
+          <t>['정치', '반도체', '투자심리']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2510,13 +2510,13 @@
         <v>-0.19</v>
       </c>
       <c r="E23" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F23" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" t="n">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="H23" t="n">
         <v>1.8</v>
@@ -2542,7 +2542,7 @@
         <v>1.99</v>
       </c>
       <c r="O23" t="n">
-        <v>69056402910</v>
+        <v>69601730945</v>
       </c>
       <c r="P23" t="n">
         <v>23500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>수도권 거점 공장 기반 건설 기초 소재 대장주로서의 언급과 함께, 일부 투자자들의 매도 및 차익실현 움직임이 관찰됨. 외국인 순매수에도 불구하고 주가 변동성이 나타나고 있음.</t>
+          <t>건설 및 개발 관련 기대감과 함께 주가 하락, 주포 의심 및 대차 물량 증가.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['건설 기초 소재', '점유율', '매물대']</t>
+          <t>['건설', '개발', '주포']</t>
         </is>
       </c>
       <c r="X23" t="n">

--- a/data/trending_integrated_20261013_14.xlsx
+++ b/data/trending_integrated_20261013_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
         <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87715901030</v>
+        <v>87720668570</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>대규모 호재성 뉴스 및 투자 주의에도 불구하고 급등세 지속, 수혜주 부각.</t>
+          <t>호남 반도체 클러스터 관련 수혜주로 급등. 연상 랠리 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호재', '수혜주', '투자주의']</t>
+          <t>['호남 반도체', '경제자유구역']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4390</v>
+        <v>4590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.71%</t>
+          <t>'+17.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>105261739258</v>
+        <v>109552990155</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -711,23 +711,23 @@
         <v>2810</v>
       </c>
       <c r="R3" t="n">
-        <v>-96000</v>
+        <v>-75000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>러시아 흑사병 테마 관련 국제약품의 치료제 부각. 신풍제약 과거 사례 비교 및 텐버거 기대. 경영권 승계 이슈도 존재.</t>
+          <t>흑사병 테마주로 부각되며 급등. 과거 신풍제약과 비교하며 텐버거 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병 테마', '치료제', '경영권 승계']</t>
+          <t>['흑사병 테마주', '치료제']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11740</v>
+        <v>11940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.05%</t>
+          <t>'+7.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G4" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>386477114665</v>
+        <v>388722291390</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -803,14 +803,14 @@
         <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>-203000</v>
+        <v>-219000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>급등락 반복, 주포 활동 의심 및 향후 상승 기대 혼재.</t>
+          <t>단기 상승 후 차익 실현 매물 출회. 이재명 테마주 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주포', '변동성']</t>
+          <t>['이재명 테마주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16960</v>
+        <v>17110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.73%</t>
+          <t>'+4.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
@@ -886,7 +886,7 @@
         <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>250187255735</v>
+        <v>251139978850</v>
       </c>
       <c r="P5" t="n">
         <v>19930</v>
@@ -895,23 +895,23 @@
         <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>30000</v>
+        <v>42000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보안주 테마 상승 기대 및 신고가 돌파 가능성 언급, 국제 정세 불안 우려.</t>
+          <t>보안주로서 강세 움직임. 전고점 돌파 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', '국제정세']</t>
+          <t>['보안주', '신고가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18180</v>
+        <v>3795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="F6" t="n">
         <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>351</v>
+        <v>148</v>
       </c>
       <c r="H6" t="n">
-        <v>27.69</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18010</v>
+        <v>3710</v>
       </c>
       <c r="K6" t="n">
-        <v>17430</v>
+        <v>3555</v>
       </c>
       <c r="L6" t="n">
-        <v>18190</v>
+        <v>4440</v>
       </c>
       <c r="M6" t="n">
-        <v>17210</v>
+        <v>3475</v>
       </c>
       <c r="N6" t="n">
-        <v>27.61</v>
+        <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>66152226765</v>
+        <v>99266405780</v>
       </c>
       <c r="P6" t="n">
-        <v>35350</v>
+        <v>6660</v>
       </c>
       <c r="Q6" t="n">
-        <v>17210</v>
+        <v>2200</v>
       </c>
       <c r="R6" t="n">
-        <v>743000</v>
+        <v>-70000</v>
       </c>
       <c r="S6" t="n">
-        <v>65000</v>
+        <v>-18000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
+          <t>러시아발 페스트 관련주로 부각되며 상승 기대감 형성. 다만, 관련 뉴스 신뢰도 및 백신 개발 여부 불확실.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 확대', '목표가']</t>
+          <t>['페스트', '러시아', '백신']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3735</v>
+        <v>18170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>146</v>
+        <v>374</v>
       </c>
       <c r="H7" t="n">
-        <v>0.91</v>
+        <v>27.69</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3710</v>
+        <v>18010</v>
       </c>
       <c r="K7" t="n">
-        <v>3555</v>
+        <v>17430</v>
       </c>
       <c r="L7" t="n">
-        <v>4440</v>
+        <v>18250</v>
       </c>
       <c r="M7" t="n">
-        <v>3475</v>
+        <v>17210</v>
       </c>
       <c r="N7" t="n">
-        <v>0.78</v>
+        <v>27.61</v>
       </c>
       <c r="O7" t="n">
-        <v>98406340445</v>
+        <v>68511228635</v>
       </c>
       <c r="P7" t="n">
-        <v>6660</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>2200</v>
+        <v>17210</v>
       </c>
       <c r="R7" t="n">
-        <v>-120000</v>
+        <v>843000</v>
       </c>
       <c r="S7" t="n">
-        <v>-18000</v>
+        <v>211000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>러시아발 페스트 관련주로 부각되며 상승 기대감 형성. 다만, 관련 뉴스 신뢰도 및 백신 개발 여부 불확실.</t>
+          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['페스트', '러시아', '백신']</t>
+          <t>['FLNG', '매출 확대', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44600</v>
+        <v>44200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'-0.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.23</v>
       </c>
       <c r="E8" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G8" t="n">
-        <v>1063</v>
+        <v>1091</v>
       </c>
       <c r="H8" t="n">
         <v>13.1</v>
@@ -1162,7 +1162,7 @@
         <v>13.33</v>
       </c>
       <c r="O8" t="n">
-        <v>32079987100</v>
+        <v>32717323650</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1171,14 +1171,14 @@
         <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>70000</v>
+        <v>90000</v>
       </c>
       <c r="S8" t="n">
-        <v>12000</v>
+        <v>17000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>간암 1차 승인 기대감으로 인한 주가 상승 전망. 공매도 세력의 움직임 및 AI 분석 기반 긍정적 전망.</t>
+          <t>간암 1차 승인 기대감으로 인한 급등 가능성 언급. 공매도 세력과의 대립.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', '승인']</t>
+          <t>['리보세라닙', '간암 1차']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,123 +1207,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16030</v>
+        <v>1563</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.16</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>171</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>452</v>
+        <v>256</v>
       </c>
       <c r="H9" t="n">
-        <v>9.630000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16090</v>
+        <v>1578</v>
       </c>
       <c r="K9" t="n">
-        <v>15190</v>
+        <v>1578</v>
       </c>
       <c r="L9" t="n">
-        <v>16050</v>
+        <v>1776</v>
       </c>
       <c r="M9" t="n">
-        <v>15100</v>
+        <v>1457</v>
       </c>
       <c r="N9" t="n">
-        <v>9.470000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>59700485815</v>
+        <v>9287905210</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2930</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>910</v>
       </c>
       <c r="R9" t="n">
-        <v>630000</v>
+        <v>116000</v>
       </c>
       <c r="S9" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>금감원 사모펀드 점검 및 공매도 관련 언급, 지수 폭락에도 주가 방어력 요구.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['금감원', '공매도', '사모펀드']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6570</v>
+        <v>15930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.05%</t>
+          <t>'-0.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.3</v>
+        <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
-        <v>681</v>
+        <v>466</v>
       </c>
       <c r="H10" t="n">
-        <v>12.27</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6640</v>
+        <v>16090</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>15190</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>16050</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="N10" t="n">
-        <v>12.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>21239000000</v>
+        <v>61071705835</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-514000</v>
+        <v>658000</v>
       </c>
       <c r="S10" t="n">
-        <v>-1000</v>
+        <v>60000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 세력의 주가 누르기 시도에도 불구하고, 금호타이어의 실적 개선 및 부지 개발 이슈로 인한 반등 기대.</t>
+          <t>금감원 사모펀드 점검 및 공매도 관련 언급, 지수 폭락에도 주가 방어력 요구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '실적', '부지']</t>
+          <t>['금감원', '공매도', '사모펀드']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,270 +1384,270 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1556</v>
+        <v>70200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-1.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="G11" t="n">
-        <v>255</v>
+        <v>768</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32</v>
+        <v>22.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1578</v>
+        <v>71500</v>
       </c>
       <c r="K11" t="n">
-        <v>1578</v>
+        <v>68400</v>
       </c>
       <c r="L11" t="n">
-        <v>1776</v>
+        <v>70700</v>
       </c>
       <c r="M11" t="n">
-        <v>1457</v>
+        <v>67300</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>22.21</v>
       </c>
       <c r="O11" t="n">
-        <v>9260902413</v>
+        <v>172964199850</v>
       </c>
       <c r="P11" t="n">
-        <v>2930</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>910</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>53000</v>
+        <v>-6000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
+          <t>원전 사업 및 정부 정책에 대한 불만 표출. 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
+          <t>['원전', '이재명']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7520</v>
+        <v>6000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.09%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.36</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>447</v>
+        <v>137</v>
       </c>
       <c r="H12" t="n">
-        <v>26.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7760</v>
+        <v>6210</v>
       </c>
       <c r="K12" t="n">
-        <v>7650</v>
+        <v>5950</v>
       </c>
       <c r="L12" t="n">
-        <v>7680</v>
+        <v>6560</v>
       </c>
       <c r="M12" t="n">
-        <v>7300</v>
+        <v>5840</v>
       </c>
       <c r="N12" t="n">
-        <v>26.37</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>25753371260</v>
+        <v>23840240325</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>11370</v>
       </c>
       <c r="Q12" t="n">
-        <v>7300</v>
+        <v>3300</v>
       </c>
       <c r="R12" t="n">
-        <v>-822000</v>
+        <v>75000</v>
       </c>
       <c r="S12" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>실적 부진 및 상장폐지 가능성 언급, 투자 확대 및 유상증자 예상.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', '투자']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6000</v>
+        <v>6550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="G13" t="n">
-        <v>132</v>
+        <v>683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6899999999999999</v>
+        <v>12.27</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6210</v>
+        <v>6810</v>
       </c>
       <c r="K13" t="n">
-        <v>5950</v>
+        <v>7150</v>
       </c>
       <c r="L13" t="n">
-        <v>6560</v>
+        <v>7160</v>
       </c>
       <c r="M13" t="n">
-        <v>5840</v>
+        <v>6440</v>
       </c>
       <c r="N13" t="n">
-        <v>0.75</v>
+        <v>12.57</v>
       </c>
       <c r="O13" t="n">
-        <v>23763173415</v>
+        <v>21453501715</v>
       </c>
       <c r="P13" t="n">
-        <v>11370</v>
+        <v>8850</v>
       </c>
       <c r="Q13" t="n">
-        <v>3300</v>
+        <v>4220</v>
       </c>
       <c r="R13" t="n">
-        <v>78000</v>
+        <v>-464000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>공매도 세력의 주가 누르기 시도에도 불구하고, 금호타이어의 실적 개선 및 부지 개발 이슈로 인한 반등 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['공매도', '실적', '부지']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,104 +1655,104 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17870</v>
+        <v>7460</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.42</v>
+        <v>-0.36</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>96</v>
+        <v>451</v>
       </c>
       <c r="H14" t="n">
-        <v>0.46</v>
+        <v>26.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18550</v>
+        <v>7760</v>
       </c>
       <c r="K14" t="n">
-        <v>17550</v>
+        <v>7650</v>
       </c>
       <c r="L14" t="n">
-        <v>19580</v>
+        <v>7680</v>
       </c>
       <c r="M14" t="n">
-        <v>17010</v>
+        <v>7300</v>
       </c>
       <c r="N14" t="n">
-        <v>0.88</v>
+        <v>26.37</v>
       </c>
       <c r="O14" t="n">
-        <v>74253082530</v>
+        <v>26230676060</v>
       </c>
       <c r="P14" t="n">
-        <v>30550</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>6100</v>
+        <v>7300</v>
       </c>
       <c r="R14" t="n">
-        <v>-36000</v>
+        <v>-908000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
+          <t>실적 부진 및 상장폐지 가능성 언급, 투자 확대 및 유상증자 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['실적', '유상증자', '투자']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12720</v>
+        <v>12800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.15%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>212</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H15" t="n">
         <v>0.3</v>
@@ -1806,7 +1806,7 @@
         <v>0.21</v>
       </c>
       <c r="O15" t="n">
-        <v>67487109150</v>
+        <v>67871044140</v>
       </c>
       <c r="P15" t="n">
         <v>28700</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차 잔고 및 공매도 관련 언급은 있으나, 투자자들은 명확한 분석 없이 주가 하락을 경험하고 있음. 매수세 유입 시 즉각적인 매도세가 나타나는 패턴이 관찰됨.</t>
+          <t>주가 하락에 대한 실망감 표현. 분석 무의미하다는 의견.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차', '공매도', '매수세']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,70 +1851,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>176400</v>
+        <v>17650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.57%</t>
+          <t>'-4.85%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-0.42</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>75.20999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>186800</v>
+        <v>18550</v>
       </c>
       <c r="K16" t="n">
-        <v>180800</v>
+        <v>17550</v>
       </c>
       <c r="L16" t="n">
-        <v>183000</v>
+        <v>19580</v>
       </c>
       <c r="M16" t="n">
-        <v>170000</v>
+        <v>17010</v>
       </c>
       <c r="N16" t="n">
-        <v>75.23</v>
+        <v>0.88</v>
       </c>
       <c r="O16" t="n">
-        <v>679131214950</v>
+        <v>74863285685</v>
       </c>
       <c r="P16" t="n">
-        <v>243500</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>70400</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>-532000</v>
+        <v>-51000</v>
       </c>
       <c r="S16" t="n">
-        <v>92000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19280</v>
+        <v>174600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.72%</t>
+          <t>'-6.53%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.39</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>312</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
-        <v>440</v>
+        <v>172</v>
       </c>
       <c r="H17" t="n">
-        <v>0.73</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>20450</v>
+        <v>186800</v>
       </c>
       <c r="K17" t="n">
-        <v>19540</v>
+        <v>180800</v>
       </c>
       <c r="L17" t="n">
-        <v>23100</v>
+        <v>183000</v>
       </c>
       <c r="M17" t="n">
-        <v>17540</v>
+        <v>170000</v>
       </c>
       <c r="N17" t="n">
-        <v>0.34</v>
+        <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>95085698115</v>
+        <v>702065938350</v>
       </c>
       <c r="P17" t="n">
-        <v>62100</v>
+        <v>243500</v>
       </c>
       <c r="Q17" t="n">
-        <v>17540</v>
+        <v>70400</v>
       </c>
       <c r="R17" t="n">
-        <v>-3000</v>
+        <v>-733000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 조작 의심 및 단기 급등락 반복, 투자자 피해 우려.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가조작', '급등락', '투자자피해']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,43 +2023,43 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14710</v>
+        <v>19080</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.42%</t>
+          <t>'-6.70%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>123</v>
+        <v>313</v>
       </c>
       <c r="F18" t="n">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="G18" t="n">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="H18" t="n">
-        <v>3.43</v>
+        <v>0.73</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15720</v>
+        <v>20450</v>
       </c>
       <c r="K18" t="n">
-        <v>14770</v>
+        <v>19540</v>
       </c>
       <c r="L18" t="n">
-        <v>15130</v>
+        <v>23100</v>
       </c>
       <c r="M18" t="n">
-        <v>14160</v>
+        <v>17540</v>
       </c>
       <c r="N18" t="n">
-        <v>3.37</v>
+        <v>0.34</v>
       </c>
       <c r="O18" t="n">
-        <v>82896653615</v>
+        <v>95881025385</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>62100</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>17540</v>
       </c>
       <c r="R18" t="n">
-        <v>79000</v>
+        <v>-1000</v>
       </c>
       <c r="S18" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록 및 외인 대량 매수에도 불구하고 주가 하락. 미국 AI 거품론 영향.</t>
+          <t>주가 조작 의심 및 단기 급등락 반복, 투자자 피해 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '외인매수', 'AI거품론']</t>
+          <t>['주가조작', '급등락', '투자자피해']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,86 +2120,86 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>233250</v>
+        <v>14630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.89%</t>
+          <t>'-6.93%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>124</v>
       </c>
       <c r="F19" t="n">
-        <v>552</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>1711</v>
+        <v>437</v>
       </c>
       <c r="H19" t="n">
-        <v>46.3</v>
+        <v>3.43</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>250500</v>
+        <v>15720</v>
       </c>
       <c r="K19" t="n">
-        <v>241500</v>
+        <v>14770</v>
       </c>
       <c r="L19" t="n">
-        <v>244000</v>
+        <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>228000</v>
+        <v>14160</v>
       </c>
       <c r="N19" t="n">
-        <v>46.35</v>
+        <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>4390999864500</v>
+        <v>84596171540</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-4524000</v>
+        <v>71000</v>
       </c>
       <c r="S19" t="n">
-        <v>383000</v>
+        <v>-9000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 급락 및 향후 반등 기대, 기술 유출 관련 언급.</t>
+          <t>3분기 실적 서프라이즈에도 불구하고 주가 하락. 미국 AI 거품론 영향.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '기술유출']</t>
+          <t>['실적 서프라이즈', '광케이블']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>71100</v>
+        <v>231500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.30%</t>
+          <t>'-7.58%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>249</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>157</v>
+        <v>545</v>
       </c>
       <c r="G20" t="n">
-        <v>761</v>
+        <v>1691</v>
       </c>
       <c r="H20" t="n">
-        <v>22.1</v>
+        <v>46.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>76700</v>
+        <v>250500</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>241500</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>244000</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="N20" t="n">
-        <v>22.21</v>
+        <v>46.35</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4524037316500</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>90200</v>
       </c>
       <c r="R20" t="n">
-        <v>85000</v>
+        <v>-5208000</v>
       </c>
       <c r="S20" t="n">
-        <v>-62000</v>
+        <v>223000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주식 시장 전반에 대한 불만과 함께 특정 인물들에 대한 비판이 제기됨. 원전 사업 관련 불확실성과 반대매매 발생 가능성이 언급되며 주가 하락 우려가 있음.</t>
+          <t>정치적 이슈로 인한 급락 및 향후 반등 기대, 기술 유출 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '반대매매', '주가 하락']</t>
+          <t>['정치', '반도체', '기술유출']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         <v>103</v>
       </c>
       <c r="G21" t="n">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>195940787740</v>
+        <v>196536744185</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2367,7 +2367,7 @@
         <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>4000</v>
+        <v>-22000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1470000</v>
+        <v>6730</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.41%</t>
+          <t>'-9.18%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>157</v>
       </c>
       <c r="F22" t="n">
-        <v>602</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
-        <v>1430</v>
+        <v>397</v>
       </c>
       <c r="H22" t="n">
-        <v>49.41</v>
+        <v>1.8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1605000</v>
+        <v>7410</v>
       </c>
       <c r="K22" t="n">
-        <v>1538000</v>
+        <v>7330</v>
       </c>
       <c r="L22" t="n">
-        <v>1554000</v>
+        <v>8040</v>
       </c>
       <c r="M22" t="n">
-        <v>1431000</v>
+        <v>6600</v>
       </c>
       <c r="N22" t="n">
-        <v>49.52</v>
+        <v>1.99</v>
       </c>
       <c r="O22" t="n">
-        <v>5925178575000</v>
+        <v>70122773435</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>23500</v>
       </c>
       <c r="Q22" t="n">
-        <v>403000</v>
+        <v>2890</v>
       </c>
       <c r="R22" t="n">
-        <v>-1103000</v>
+        <v>-277000</v>
       </c>
       <c r="S22" t="n">
-        <v>137000</v>
+        <v>-218000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 외부 요인으로 인한 주가 하락, 투자 심리 위축.</t>
+          <t>건설 기초소재 대장주로 언급되나, 매도 및 하락 의견 다수.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '투자심리']</t>
+          <t>['건설 기초소재', '신도시개발']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6670</v>
+        <v>1456000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.99%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>154</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>66</v>
+        <v>589</v>
       </c>
       <c r="G23" t="n">
-        <v>382</v>
+        <v>1422</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8</v>
+        <v>49.41</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7410</v>
+        <v>1605000</v>
       </c>
       <c r="K23" t="n">
-        <v>7330</v>
+        <v>1538000</v>
       </c>
       <c r="L23" t="n">
-        <v>8040</v>
+        <v>1554000</v>
       </c>
       <c r="M23" t="n">
-        <v>6600</v>
+        <v>1431000</v>
       </c>
       <c r="N23" t="n">
-        <v>1.99</v>
+        <v>49.52</v>
       </c>
       <c r="O23" t="n">
-        <v>69601730945</v>
+        <v>6077859034000</v>
       </c>
       <c r="P23" t="n">
-        <v>23500</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>2890</v>
+        <v>403000</v>
       </c>
       <c r="R23" t="n">
-        <v>-286000</v>
+        <v>-1301000</v>
       </c>
       <c r="S23" t="n">
-        <v>-184000</v>
+        <v>114000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>건설 및 개발 관련 기대감과 함께 주가 하락, 주포 의심 및 대차 물량 증가.</t>
+          <t>SK하이닉스의 국내 투자 및 경영진에 대한 비판적 의견.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['건설', '개발', '주포']</t>
+          <t>['반도체', '국정농단']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_14.xlsx
+++ b/data/trending_integrated_20261013_14.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.88%</t>
+          <t>'+67.88%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F2" t="n">
         <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6760</v>
+        <v>5230</v>
       </c>
       <c r="K2" t="n">
-        <v>7530</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>8780</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>7250</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87720668570</v>
+        <v>87724000000</v>
       </c>
       <c r="P2" t="n">
-        <v>10300</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>952</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-105000</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4590</v>
+        <v>4560</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.84%</t>
+          <t>'+17.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>109552990155</v>
+        <v>114439650733</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흑사병 테마주로 부각되며 급등. 과거 신풍제약과 비교하며 텐버거 기대.</t>
+          <t>흑사병 테마 관련주로 신풍제약과 비교. 뉴스 언급 시 급등 가능성 제시하나, 진위 여부 불확실.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병 테마주', '치료제']</t>
+          <t>['흑사병 테마', '치료제', '뉴스']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11940</v>
+        <v>11980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.86%</t>
+          <t>'+8.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="F4" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G4" t="n">
-        <v>524</v>
+        <v>541</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>388722291390</v>
+        <v>392304340500</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>단기 상승 후 차익 실현 매물 출회. 이재명 테마주 언급.</t>
+          <t>이재명 테마주로 언급되며 역대급 거래량 기록. 단기 시세차익 후 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['이재명 테마주']</t>
+          <t>['이재명 테마주', '거래량', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17110</v>
+        <v>17070</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.65%</t>
+          <t>'+4.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>251139978850</v>
+        <v>252034758935</v>
       </c>
       <c r="P5" t="n">
         <v>19930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3795</v>
+        <v>3810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H6" t="n">
         <v>0.91</v>
@@ -978,7 +978,7 @@
         <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>99266405780</v>
+        <v>99894877058</v>
       </c>
       <c r="P6" t="n">
         <v>6660</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>러시아발 페스트 관련주로 부각되며 상승 기대감 형성. 다만, 관련 뉴스 신뢰도 및 백신 개발 여부 불확실.</t>
+          <t>흑사병 테마 관련 언급과 함께 독감, 코로나 백신 관련 내용 혼재. 대세 상승 시작 주장.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['페스트', '러시아', '백신']</t>
+          <t>['흑사병 테마', '독감', '코로나 백신']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18170</v>
+        <v>18200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.89%</t>
+          <t>'+1.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
         <v>374</v>
@@ -1070,7 +1070,7 @@
         <v>27.61</v>
       </c>
       <c r="O7" t="n">
-        <v>68511228635</v>
+        <v>71186918940</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성중공업 FLNG 매출 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 금지 및 주주 환원 정책 요구.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 언급. 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 확대', '목표가']</t>
+          <t>['FLNG', '매출 전망', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44200</v>
+        <v>1584</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.23</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>242</v>
+        <v>92</v>
       </c>
       <c r="F8" t="n">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>1091</v>
+        <v>256</v>
       </c>
       <c r="H8" t="n">
-        <v>13.1</v>
+        <v>0.32</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,235 +1147,235 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>44400</v>
+        <v>1578</v>
       </c>
       <c r="K8" t="n">
-        <v>43300</v>
+        <v>1578</v>
       </c>
       <c r="L8" t="n">
-        <v>44850</v>
+        <v>1776</v>
       </c>
       <c r="M8" t="n">
-        <v>42250</v>
+        <v>1457</v>
       </c>
       <c r="N8" t="n">
-        <v>13.33</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>32717323650</v>
+        <v>9350525403</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>2930</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>910</v>
       </c>
       <c r="R8" t="n">
-        <v>90000</v>
+        <v>116000</v>
       </c>
       <c r="S8" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>간암 1차 승인 기대감으로 인한 급등 가능성 언급. 공매도 세력과의 대립.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['리보세라닙', '간암 1차']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1563</v>
+        <v>15950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'-0.87%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="G9" t="n">
-        <v>256</v>
+        <v>498</v>
       </c>
       <c r="H9" t="n">
-        <v>0.32</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1578</v>
+        <v>16090</v>
       </c>
       <c r="K9" t="n">
-        <v>1578</v>
+        <v>15190</v>
       </c>
       <c r="L9" t="n">
-        <v>1776</v>
+        <v>16050</v>
       </c>
       <c r="M9" t="n">
-        <v>1457</v>
+        <v>15100</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>9287905210</v>
+        <v>62251461505</v>
       </c>
       <c r="P9" t="n">
-        <v>2930</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>910</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>116000</v>
+        <v>658000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
+          <t>금감원의 사모펀드 점검 및 공매도 관련 언급. 시세 조정 및 매집 가능성 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
+          <t>['사모펀드', '공매도', '시세조정']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15930</v>
+        <v>43900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.99%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="E10" t="n">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="G10" t="n">
-        <v>466</v>
+        <v>1098</v>
       </c>
       <c r="H10" t="n">
-        <v>9.630000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16090</v>
+        <v>44400</v>
       </c>
       <c r="K10" t="n">
-        <v>15190</v>
+        <v>43300</v>
       </c>
       <c r="L10" t="n">
-        <v>16050</v>
+        <v>44850</v>
       </c>
       <c r="M10" t="n">
-        <v>15100</v>
+        <v>42250</v>
       </c>
       <c r="N10" t="n">
-        <v>9.470000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="O10" t="n">
-        <v>61071705835</v>
+        <v>33138611425</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>658000</v>
+        <v>90000</v>
       </c>
       <c r="S10" t="n">
-        <v>60000</v>
+        <v>17000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>금감원 사모펀드 점검 및 공매도 관련 언급, 지수 폭락에도 주가 방어력 요구.</t>
+          <t>간암 1차 승인 기대감으로 인한 급등 가능성 언급. 공매도 세력과의 대립.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['금감원', '공매도', '사모펀드']</t>
+          <t>['리보세라닙', '간암 1차']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70200</v>
+        <v>70000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.82%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.11</v>
       </c>
       <c r="E11" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G11" t="n">
-        <v>768</v>
+        <v>786</v>
       </c>
       <c r="H11" t="n">
         <v>22.1</v>
@@ -1438,7 +1438,7 @@
         <v>22.21</v>
       </c>
       <c r="O11" t="n">
-        <v>172964199850</v>
+        <v>176707020850</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>원전 사업 및 정부 정책에 대한 불만 표출. 주가 하락에 대한 우려.</t>
+          <t>정치권의 주식 시장 개입 및 정책 실패로 인한 투자자 손실 우려. 원전 관련주로서의 기대감과 더불어 반대매매 및 신용 물량 부담.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '이재명']</t>
+          <t>['원전', '반대매매', '신용 물량']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6000</v>
+        <v>5990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-3.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H12" t="n">
         <v>0.6899999999999999</v>
@@ -1530,7 +1530,7 @@
         <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>23840240325</v>
+        <v>23922586865</v>
       </c>
       <c r="P12" t="n">
         <v>11370</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6550</v>
+        <v>7480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.3</v>
+        <v>-0.36</v>
       </c>
       <c r="E13" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F13" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>683</v>
+        <v>452</v>
       </c>
       <c r="H13" t="n">
-        <v>12.27</v>
+        <v>26.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6810</v>
+        <v>7760</v>
       </c>
       <c r="K13" t="n">
-        <v>7150</v>
+        <v>7650</v>
       </c>
       <c r="L13" t="n">
-        <v>7160</v>
+        <v>7680</v>
       </c>
       <c r="M13" t="n">
-        <v>6440</v>
+        <v>7300</v>
       </c>
       <c r="N13" t="n">
-        <v>12.57</v>
+        <v>26.37</v>
       </c>
       <c r="O13" t="n">
-        <v>21453501715</v>
+        <v>26865972660</v>
       </c>
       <c r="P13" t="n">
-        <v>8850</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>4220</v>
+        <v>7300</v>
       </c>
       <c r="R13" t="n">
-        <v>-464000</v>
+        <v>-908000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 세력의 주가 누르기 시도에도 불구하고, 금호타이어의 실적 개선 및 부지 개발 이슈로 인한 반등 기대.</t>
+          <t>아이폰 패널 출하량 감소 및 부채 상환 위한 유상증자 예상. FLiPP 투자 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '실적', '부지']</t>
+          <t>['아이폰', '유상증자', 'FLiPP 투자']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7460</v>
+        <v>6560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.36</v>
+        <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="G14" t="n">
-        <v>451</v>
+        <v>680</v>
       </c>
       <c r="H14" t="n">
-        <v>26.01</v>
+        <v>12.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7760</v>
+        <v>6810</v>
       </c>
       <c r="K14" t="n">
-        <v>7650</v>
+        <v>7150</v>
       </c>
       <c r="L14" t="n">
-        <v>7680</v>
+        <v>7160</v>
       </c>
       <c r="M14" t="n">
-        <v>7300</v>
+        <v>6440</v>
       </c>
       <c r="N14" t="n">
-        <v>26.37</v>
+        <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>26230676060</v>
+        <v>21710825305</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>8850</v>
       </c>
       <c r="Q14" t="n">
-        <v>7300</v>
+        <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>-908000</v>
+        <v>-464000</v>
       </c>
       <c r="S14" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 부진 및 상장폐지 가능성 언급, 투자 확대 및 유상증자 예상.</t>
+          <t>영업이익 및 순이익 언급하며 저가 매수 시점 주장. 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '유상증자', '투자']</t>
+          <t>['영업이익', '공매도', '부지 매각']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12800</v>
+        <v>17610</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-5.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="E15" t="n">
-        <v>212</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>306</v>
+        <v>102</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13410</v>
+        <v>18550</v>
       </c>
       <c r="K15" t="n">
-        <v>13260</v>
+        <v>17550</v>
       </c>
       <c r="L15" t="n">
-        <v>14580</v>
+        <v>19580</v>
       </c>
       <c r="M15" t="n">
-        <v>12680</v>
+        <v>17010</v>
       </c>
       <c r="N15" t="n">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="O15" t="n">
-        <v>67871044140</v>
+        <v>75406896120</v>
       </c>
       <c r="P15" t="n">
-        <v>28700</v>
+        <v>30550</v>
       </c>
       <c r="Q15" t="n">
-        <v>11600</v>
+        <v>6100</v>
       </c>
       <c r="R15" t="n">
-        <v>31000</v>
+        <v>-51000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 실망감 표현. 분석 무의미하다는 의견.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,51 +1831,51 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17650</v>
+        <v>12710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.85%</t>
+          <t>'-5.22%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.42</v>
+        <v>0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>312</v>
       </c>
       <c r="H16" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18550</v>
+        <v>13410</v>
       </c>
       <c r="K16" t="n">
-        <v>17550</v>
+        <v>13260</v>
       </c>
       <c r="L16" t="n">
-        <v>19580</v>
+        <v>14580</v>
       </c>
       <c r="M16" t="n">
-        <v>17010</v>
+        <v>12680</v>
       </c>
       <c r="N16" t="n">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="O16" t="n">
-        <v>74863285685</v>
+        <v>68324231180</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>28700</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>11600</v>
       </c>
       <c r="R16" t="n">
-        <v>-51000</v>
+        <v>31000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
+          <t>공매도 및 대차 잔고 증가 속에 주가 하락 지속. 투자자들 사이에서 주가 조작 및 세력 개입 의혹 제기, 객관적인 분석보다는 감정적 토로.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['공매도', '대차 잔고', '주가 조작']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174600</v>
+        <v>173700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.53%</t>
+          <t>'-7.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H17" t="n">
         <v>75.20999999999999</v>
@@ -1990,7 +1990,7 @@
         <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>702065938350</v>
+        <v>721441684300</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19080</v>
+        <v>14590</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.70%</t>
+          <t>'-7.19%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.39</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>313</v>
+        <v>125</v>
       </c>
       <c r="F18" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="H18" t="n">
-        <v>0.73</v>
+        <v>3.43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>20450</v>
+        <v>15720</v>
       </c>
       <c r="K18" t="n">
-        <v>19540</v>
+        <v>14770</v>
       </c>
       <c r="L18" t="n">
-        <v>23100</v>
+        <v>15130</v>
       </c>
       <c r="M18" t="n">
-        <v>17540</v>
+        <v>14160</v>
       </c>
       <c r="N18" t="n">
-        <v>0.34</v>
+        <v>3.37</v>
       </c>
       <c r="O18" t="n">
-        <v>95881025385</v>
+        <v>85973868710</v>
       </c>
       <c r="P18" t="n">
-        <v>62100</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>17540</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-1000</v>
+        <v>71000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 의심 및 단기 급등락 반복, 투자자 피해 우려.</t>
+          <t>3분기 어닝 서프라이즈 기록, 매출액 및 영업이익 전분기 대비 큰 폭 증가. 미국 업체 기술력 우위 및 AI 거품론에도 불구하고 외인 대량 매수 관측.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '급등락', '투자자피해']</t>
+          <t>['어닝 서프라이즈', '광케이블', '외인 매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,86 +2120,86 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14630</v>
+        <v>230750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.93%</t>
+          <t>'-7.88%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E19" t="n">
-        <v>124</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
+        <v>549</v>
       </c>
       <c r="G19" t="n">
-        <v>437</v>
+        <v>1647</v>
       </c>
       <c r="H19" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K19" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L19" t="n">
-        <v>15130</v>
+        <v>244000</v>
       </c>
       <c r="M19" t="n">
-        <v>14160</v>
+        <v>228000</v>
       </c>
       <c r="N19" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O19" t="n">
-        <v>84596171540</v>
+        <v>4647835653500</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R19" t="n">
-        <v>71000</v>
+        <v>-5208000</v>
       </c>
       <c r="S19" t="n">
-        <v>-9000</v>
+        <v>223000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 실적 서프라이즈에도 불구하고 주가 하락. 미국 AI 거품론 영향.</t>
+          <t>정치적 논쟁이 주를 이루며, 주가 하락에 대한 정치적 책임론 제기. 기술 유출 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적 서프라이즈', '광케이블']</t>
+          <t>['정치', '주가 하락', '기술 유출']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>231500</v>
+        <v>12280</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.58%</t>
+          <t>'-8.36%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.05</v>
+        <v>-1.01</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>188</v>
       </c>
       <c r="F20" t="n">
-        <v>545</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
-        <v>1691</v>
+        <v>448</v>
       </c>
       <c r="H20" t="n">
-        <v>46.3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>250500</v>
+        <v>13400</v>
       </c>
       <c r="K20" t="n">
-        <v>241500</v>
+        <v>13750</v>
       </c>
       <c r="L20" t="n">
-        <v>244000</v>
+        <v>15390</v>
       </c>
       <c r="M20" t="n">
-        <v>228000</v>
+        <v>11980</v>
       </c>
       <c r="N20" t="n">
-        <v>46.35</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
-        <v>4524037316500</v>
+        <v>197075600870</v>
       </c>
       <c r="P20" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>90200</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>-5208000</v>
+        <v>-22000</v>
       </c>
       <c r="S20" t="n">
-        <v>223000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 급락 및 향후 반등 기대, 기술 유출 관련 언급.</t>
+          <t>주포의 움직임과 공매도 관련 언급. 반도체 호남 클러스터 관련 내용 혼재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '기술유출']</t>
+          <t>['주포', '공매도', '반도체 클러스터']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12310</v>
+        <v>18650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.13%</t>
+          <t>'-8.80%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.01</v>
+        <v>0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="G21" t="n">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13400</v>
+        <v>20450</v>
       </c>
       <c r="K21" t="n">
-        <v>13750</v>
+        <v>19540</v>
       </c>
       <c r="L21" t="n">
-        <v>15390</v>
+        <v>23100</v>
       </c>
       <c r="M21" t="n">
-        <v>11980</v>
+        <v>17540</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>0.34</v>
       </c>
       <c r="O21" t="n">
-        <v>196536744185</v>
+        <v>97369996335</v>
       </c>
       <c r="P21" t="n">
-        <v>19380</v>
+        <v>62100</v>
       </c>
       <c r="Q21" t="n">
-        <v>3200</v>
+        <v>17540</v>
       </c>
       <c r="R21" t="n">
-        <v>-22000</v>
+        <v>-1000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주포 활동 의심 및 목표가 제시, 경쟁사 상승 대비 주가 부진 언급.</t>
+          <t>보호예수 물량 및 외부 조달 판매 의혹 제기. 단기 급등락 반복 및 주가 조작 의심, 투자자들의 혼란과 불신 심화.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주포', '목표가', '경쟁사']</t>
+          <t>['보호예수', '주가 조작', '단기 급등락']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,90 +2396,90 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6730</v>
+        <v>1447000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.18%</t>
+          <t>'-9.84%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>157</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>68</v>
+        <v>586</v>
       </c>
       <c r="G22" t="n">
-        <v>397</v>
+        <v>1360</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8</v>
+        <v>49.41</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7410</v>
+        <v>1605000</v>
       </c>
       <c r="K22" t="n">
-        <v>7330</v>
+        <v>1538000</v>
       </c>
       <c r="L22" t="n">
-        <v>8040</v>
+        <v>1554000</v>
       </c>
       <c r="M22" t="n">
-        <v>6600</v>
+        <v>1431000</v>
       </c>
       <c r="N22" t="n">
-        <v>1.99</v>
+        <v>49.52</v>
       </c>
       <c r="O22" t="n">
-        <v>70122773435</v>
+        <v>6264893914000</v>
       </c>
       <c r="P22" t="n">
-        <v>23500</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>2890</v>
+        <v>403000</v>
       </c>
       <c r="R22" t="n">
-        <v>-277000</v>
+        <v>-1301000</v>
       </c>
       <c r="S22" t="n">
-        <v>-218000</v>
+        <v>114000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>건설 기초소재 대장주로 언급되나, 매도 및 하락 의견 다수.</t>
+          <t>정치적 이슈 및 호남 투자 관련 부정적 언급이 주를 이룸. 최태원 관련 비판.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['건설 기초소재', '신도시개발']</t>
+          <t>['정치', '호남 투자', '최태원']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1456000</v>
+        <v>6660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.28%</t>
+          <t>'-10.12%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>159</v>
       </c>
       <c r="F23" t="n">
-        <v>589</v>
+        <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>1422</v>
+        <v>400</v>
       </c>
       <c r="H23" t="n">
-        <v>49.41</v>
+        <v>1.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1605000</v>
+        <v>7410</v>
       </c>
       <c r="K23" t="n">
-        <v>1538000</v>
+        <v>7330</v>
       </c>
       <c r="L23" t="n">
-        <v>1554000</v>
+        <v>8040</v>
       </c>
       <c r="M23" t="n">
-        <v>1431000</v>
+        <v>6600</v>
       </c>
       <c r="N23" t="n">
-        <v>49.52</v>
+        <v>1.99</v>
       </c>
       <c r="O23" t="n">
-        <v>6077859034000</v>
+        <v>70543004105</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>23500</v>
       </c>
       <c r="Q23" t="n">
-        <v>403000</v>
+        <v>2890</v>
       </c>
       <c r="R23" t="n">
-        <v>-1301000</v>
+        <v>-277000</v>
       </c>
       <c r="S23" t="n">
-        <v>114000</v>
+        <v>-218000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>SK하이닉스의 국내 투자 및 경영진에 대한 비판적 의견.</t>
+          <t>수도권 거점 공장 보유 및 건설 기초 소재 대장주 명성에도 불구하고, 개인 투자자 매도 및 대차 거래 증가 우려. 주포 움직임에 대한 논란.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['반도체', '국정농단']</t>
+          <t>['건설 기초 소재', '주포', '대차 거래']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>038500</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_14.xlsx
+++ b/data/trending_integrated_20261013_14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+67.88%</t>
+          <t>'+29.88%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F2" t="n">
         <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5230</v>
+        <v>6760</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>7530</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>7250</v>
       </c>
       <c r="N2" t="n">
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87724000000</v>
+        <v>87746859310</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
         <v>-105000</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4560</v>
+        <v>4795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.07%</t>
+          <t>'+23.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.53</v>
       </c>
       <c r="E3" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H3" t="n">
         <v>2.05</v>
@@ -693,7 +693,7 @@
         <v>3730</v>
       </c>
       <c r="L3" t="n">
-        <v>4770</v>
+        <v>4795</v>
       </c>
       <c r="M3" t="n">
         <v>3650</v>
@@ -702,7 +702,7 @@
         <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>114439650733</v>
+        <v>124139369538</v>
       </c>
       <c r="P3" t="n">
         <v>5470</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련주로 신풍제약과 비교. 뉴스 언급 시 급등 가능성 제시하나, 진위 여부 불확실.</t>
+          <t>러시아 흑사병 테마 관련주로 급등하며, 과거 신풍제약 사례에 비견됨. 일부에서는 경영권 승계 및 치료제 관련 뉴스를 기대하며 매수를 독려하는 의견과, 개미 털기 및 속지 말라는 경고 의견이 혼재함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병 테마', '치료제', '뉴스']</t>
+          <t>['흑사병 테마', '치료제', '경영권 승계']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11980</v>
+        <v>11710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.22%</t>
+          <t>'+5.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F4" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G4" t="n">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>392304340500</v>
+        <v>395035822770</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>이재명 테마주로 언급되며 역대급 거래량 기록. 단기 시세차익 후 하락 가능성 언급.</t>
+          <t>이재명 테마주로 언급되며 변동성이 크고, 일부는 매도 성공을 알리는 글도 존재함. 주포의 움직임과 차트 패턴을 언급하며 단기적인 상승 가능성을 기대하는 의견도 있음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['이재명 테마주', '거래량', '주포']</t>
+          <t>['이재명 테마주', '주포', '패턴']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17070</v>
+        <v>17150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.40%</t>
+          <t>'+4.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F5" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
@@ -886,7 +886,7 @@
         <v>1.13</v>
       </c>
       <c r="O5" t="n">
-        <v>252034758935</v>
+        <v>252659607920</v>
       </c>
       <c r="P5" t="n">
         <v>19930</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보안주로서 강세 움직임. 전고점 돌파 기대감.</t>
+          <t>보안주 테마의 대장주로 언급되며 신고가 돌파 및 10% 이상 상승을 기대하는 의견이 많음. 디지털 자산 관련 내용의 조만간 발표 가능성을 언급하며 상승 모멘텀을 기대하고 있음.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '신고가']</t>
+          <t>['보안주', '신고가', '디지털 자산']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3810</v>
+        <v>3890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+4.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H6" t="n">
         <v>0.91</v>
@@ -978,7 +978,7 @@
         <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>99894877058</v>
+        <v>101439660786</v>
       </c>
       <c r="P6" t="n">
         <v>6660</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>롯데손해보험</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18200</v>
+        <v>2435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.05%</t>
+          <t>'+4.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H7" t="n">
-        <v>27.69</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18010</v>
+        <v>2330</v>
       </c>
       <c r="K7" t="n">
-        <v>17430</v>
+        <v>2400</v>
       </c>
       <c r="L7" t="n">
-        <v>18250</v>
+        <v>2690</v>
       </c>
       <c r="M7" t="n">
-        <v>17210</v>
+        <v>2110</v>
       </c>
       <c r="N7" t="n">
-        <v>27.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>71186918940</v>
+        <v>33370664124</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>3280</v>
       </c>
       <c r="Q7" t="n">
-        <v>17210</v>
+        <v>1576</v>
       </c>
       <c r="R7" t="n">
-        <v>843000</v>
+        <v>-47000</v>
       </c>
       <c r="S7" t="n">
-        <v>211000</v>
+        <v>41000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 언급. 공매도 금지 요구.</t>
+          <t>신한금융의 100% 지분 인수 확정 및 목표가 만원 제시 등 인수 관련 호재가 집중적으로 언급됨. 신한지주와의 합병 및 시너지 극대화에 대한 기대감이 높으며, 주주들은 확정 수익임을 강조함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 전망', '목표가']</t>
+          <t>['신한금융 인수', '공개매수', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,274 +1108,274 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000400</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1584</v>
+        <v>18220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+1.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>256</v>
+        <v>403</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>27.69</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1578</v>
+        <v>18010</v>
       </c>
       <c r="K8" t="n">
-        <v>1578</v>
+        <v>17430</v>
       </c>
       <c r="L8" t="n">
-        <v>1776</v>
+        <v>18250</v>
       </c>
       <c r="M8" t="n">
-        <v>1457</v>
+        <v>17210</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>9350525403</v>
+        <v>73086823065</v>
       </c>
       <c r="P8" t="n">
-        <v>2930</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>910</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>116000</v>
+        <v>843000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>211000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
+          <t>FLNG 매출 3.2조 확대 전망 및 증권사 목표가 42,000원 등 긍정적인 뉴스 언급. 일부에서는 공매도 금지 및 주주 환원 정책 발표를 요구하며, 기술적 반등 가능성을 언급하는 의견도 있음.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
+          <t>['FLNG 매출', '목표가', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15950</v>
+        <v>1573</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.87%</t>
+          <t>'-0.32%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.16</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>498</v>
+        <v>256</v>
       </c>
       <c r="H9" t="n">
-        <v>9.630000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16090</v>
+        <v>1578</v>
       </c>
       <c r="K9" t="n">
-        <v>15190</v>
+        <v>1578</v>
       </c>
       <c r="L9" t="n">
-        <v>16050</v>
+        <v>1776</v>
       </c>
       <c r="M9" t="n">
-        <v>15100</v>
+        <v>1457</v>
       </c>
       <c r="N9" t="n">
-        <v>9.470000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>62251461505</v>
+        <v>9377445464</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>2930</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>910</v>
       </c>
       <c r="R9" t="n">
-        <v>658000</v>
+        <v>116000</v>
       </c>
       <c r="S9" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>금감원의 사모펀드 점검 및 공매도 관련 언급. 시세 조정 및 매집 가능성 제기.</t>
+          <t>장성지역 경제자유구역 추가 편입 및 메가프로젝트 투자 기대. 대주주 매도 후 재매수 및 주도주 수혜 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['사모펀드', '공매도', '시세조정']</t>
+          <t>['경제자유구역', '메가프로젝트', '주도주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43900</v>
+        <v>15920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-1.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.23</v>
+        <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="F10" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>1098</v>
+        <v>503</v>
       </c>
       <c r="H10" t="n">
-        <v>13.1</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>44400</v>
+        <v>16090</v>
       </c>
       <c r="K10" t="n">
-        <v>43300</v>
+        <v>15190</v>
       </c>
       <c r="L10" t="n">
-        <v>44850</v>
+        <v>16050</v>
       </c>
       <c r="M10" t="n">
-        <v>42250</v>
+        <v>15100</v>
       </c>
       <c r="N10" t="n">
-        <v>13.33</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>33138611425</v>
+        <v>63264001335</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>90000</v>
+        <v>658000</v>
       </c>
       <c r="S10" t="n">
-        <v>17000</v>
+        <v>60000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>간암 1차 승인 기대감으로 인한 급등 가능성 언급. 공매도 세력과의 대립.</t>
+          <t>금감원의 사모펀드 점검 및 공매도 관련 언급. 시세 조정 및 매집 가능성 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보세라닙', '간암 1차']</t>
+          <t>['사모펀드', '공매도', '시세조정']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70000</v>
+        <v>43850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.23</v>
       </c>
       <c r="E11" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F11" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="G11" t="n">
-        <v>786</v>
+        <v>1120</v>
       </c>
       <c r="H11" t="n">
-        <v>22.1</v>
+        <v>13.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71500</v>
+        <v>44400</v>
       </c>
       <c r="K11" t="n">
-        <v>68400</v>
+        <v>43300</v>
       </c>
       <c r="L11" t="n">
-        <v>70700</v>
+        <v>44850</v>
       </c>
       <c r="M11" t="n">
-        <v>67300</v>
+        <v>42250</v>
       </c>
       <c r="N11" t="n">
-        <v>22.21</v>
+        <v>13.33</v>
       </c>
       <c r="O11" t="n">
-        <v>176707020850</v>
+        <v>33546470900</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-6000</v>
+        <v>90000</v>
       </c>
       <c r="S11" t="n">
-        <v>-37000</v>
+        <v>17000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치권의 주식 시장 개입 및 정책 실패로 인한 투자자 손실 우려. 원전 관련주로서의 기대감과 더불어 반대매매 및 신용 물량 부담.</t>
+          <t>간암 1차 치료제 승인 기대감 및 공매도 세력과의 공방 예상. AI 분석 기반 긍정 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '반대매매', '신용 물량']</t>
+          <t>['간암 치료제', '공매도', 'AI 분석']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5990</v>
+        <v>70000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>260</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="G12" t="n">
-        <v>141</v>
+        <v>792</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6899999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6210</v>
+        <v>71500</v>
       </c>
       <c r="K12" t="n">
-        <v>5950</v>
+        <v>68400</v>
       </c>
       <c r="L12" t="n">
-        <v>6560</v>
+        <v>70700</v>
       </c>
       <c r="M12" t="n">
-        <v>5840</v>
+        <v>67300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>22.21</v>
       </c>
       <c r="O12" t="n">
-        <v>23922586865</v>
+        <v>179904856050</v>
       </c>
       <c r="P12" t="n">
-        <v>11370</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>3300</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>75000</v>
+        <v>-6000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-37000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>정치권의 주식 시장 개입 및 정책 실패로 인한 투자자 손실 우려. 원전 관련주로서의 기대감과 더불어 반대매매 및 신용 물량 부담.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['원전', '반대매매', '신용 물량']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,104 +1563,104 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7480</v>
+        <v>6000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.36</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>452</v>
+        <v>144</v>
       </c>
       <c r="H13" t="n">
-        <v>26.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7760</v>
+        <v>6210</v>
       </c>
       <c r="K13" t="n">
-        <v>7650</v>
+        <v>5950</v>
       </c>
       <c r="L13" t="n">
-        <v>7680</v>
+        <v>6560</v>
       </c>
       <c r="M13" t="n">
-        <v>7300</v>
+        <v>5840</v>
       </c>
       <c r="N13" t="n">
-        <v>26.37</v>
+        <v>0.75</v>
       </c>
       <c r="O13" t="n">
-        <v>26865972660</v>
+        <v>24024916300</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>11370</v>
       </c>
       <c r="Q13" t="n">
-        <v>7300</v>
+        <v>3300</v>
       </c>
       <c r="R13" t="n">
-        <v>-908000</v>
+        <v>75000</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아이폰 패널 출하량 감소 및 부채 상환 위한 유상증자 예상. FLiPP 투자 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['아이폰', '유상증자', 'FLiPP 투자']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6560</v>
+        <v>6580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>88</v>
       </c>
       <c r="G14" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="H14" t="n">
         <v>12.27</v>
@@ -1714,7 +1714,7 @@
         <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>21710825305</v>
+        <v>21868931365</v>
       </c>
       <c r="P14" t="n">
         <v>8850</v>
@@ -1759,123 +1759,123 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17610</v>
+        <v>7470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.07%</t>
+          <t>'-3.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.42</v>
+        <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G15" t="n">
-        <v>102</v>
+        <v>462</v>
       </c>
       <c r="H15" t="n">
-        <v>0.46</v>
+        <v>26.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18550</v>
+        <v>7760</v>
       </c>
       <c r="K15" t="n">
-        <v>17550</v>
+        <v>7650</v>
       </c>
       <c r="L15" t="n">
-        <v>19580</v>
+        <v>7680</v>
       </c>
       <c r="M15" t="n">
-        <v>17010</v>
+        <v>7300</v>
       </c>
       <c r="N15" t="n">
-        <v>0.88</v>
+        <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>75406896120</v>
+        <v>27270450660</v>
       </c>
       <c r="P15" t="n">
-        <v>30550</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>6100</v>
+        <v>7300</v>
       </c>
       <c r="R15" t="n">
-        <v>-51000</v>
+        <v>-908000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
+          <t>아이폰 패널 출하량 감소 및 부채 상환 위한 유상증자 예상. FLiPP 투자 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['아이폰', '유상증자', 'FLiPP 투자']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12710</v>
+        <v>17610</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.22%</t>
+          <t>'-5.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="E16" t="n">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>312</v>
+        <v>105</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,323 +1883,323 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13410</v>
+        <v>18550</v>
       </c>
       <c r="K16" t="n">
-        <v>13260</v>
+        <v>17550</v>
       </c>
       <c r="L16" t="n">
-        <v>14580</v>
+        <v>19580</v>
       </c>
       <c r="M16" t="n">
-        <v>12680</v>
+        <v>17010</v>
       </c>
       <c r="N16" t="n">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="O16" t="n">
-        <v>68324231180</v>
+        <v>76237814125</v>
       </c>
       <c r="P16" t="n">
-        <v>28700</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>11600</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>31000</v>
+        <v>-51000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 및 대차 잔고 증가 속에 주가 하락 지속. 투자자들 사이에서 주가 조작 및 세력 개입 의혹 제기, 객관적인 분석보다는 감정적 토로.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 부각. AI 해킹 관련 우려 및 떡상 기대감 공존. 매집 정황 및 거래량 아쉬움 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '대차 잔고', '주가 조작']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>173700</v>
+        <v>12620</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.01%</t>
+          <t>'-5.89%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="G17" t="n">
-        <v>181</v>
+        <v>318</v>
       </c>
       <c r="H17" t="n">
-        <v>75.20999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>186800</v>
+        <v>13410</v>
       </c>
       <c r="K17" t="n">
-        <v>180800</v>
+        <v>13260</v>
       </c>
       <c r="L17" t="n">
-        <v>183000</v>
+        <v>14580</v>
       </c>
       <c r="M17" t="n">
-        <v>170000</v>
+        <v>12620</v>
       </c>
       <c r="N17" t="n">
-        <v>75.23</v>
+        <v>0.21</v>
       </c>
       <c r="O17" t="n">
-        <v>721441684300</v>
+        <v>68881524040</v>
       </c>
       <c r="P17" t="n">
-        <v>243500</v>
+        <v>28700</v>
       </c>
       <c r="Q17" t="n">
-        <v>70400</v>
+        <v>11600</v>
       </c>
       <c r="R17" t="n">
-        <v>-733000</v>
+        <v>31000</v>
       </c>
       <c r="S17" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
+          <t>공매도 및 대차 관련 언급과 함께 분석의 무의미함을 주장하는 의견이 있음. 주포의 움직임에 대한 불신과 함께 주가 하락 및 매도세를 언급하며 부정적인 전망을 제시하는 글이 많음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가하락', '시장붕괴', '외인매수']</t>
+          <t>['공매도', '대차', '주포']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14590</v>
+        <v>173400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.19%</t>
+          <t>'-7.17%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>444</v>
+        <v>180</v>
       </c>
       <c r="H18" t="n">
-        <v>3.43</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15720</v>
+        <v>186800</v>
       </c>
       <c r="K18" t="n">
-        <v>14770</v>
+        <v>180800</v>
       </c>
       <c r="L18" t="n">
-        <v>15130</v>
+        <v>183000</v>
       </c>
       <c r="M18" t="n">
-        <v>14160</v>
+        <v>170000</v>
       </c>
       <c r="N18" t="n">
-        <v>3.37</v>
+        <v>75.23</v>
       </c>
       <c r="O18" t="n">
-        <v>85973868710</v>
+        <v>739339640000</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>243500</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>70400</v>
       </c>
       <c r="R18" t="n">
-        <v>71000</v>
+        <v>-733000</v>
       </c>
       <c r="S18" t="n">
-        <v>-9000</v>
+        <v>99000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록, 매출액 및 영업이익 전분기 대비 큰 폭 증가. 미국 업체 기술력 우위 및 AI 거품론에도 불구하고 외인 대량 매수 관측.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광케이블', '외인 매수']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>230750</v>
+        <v>14590</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.88%</t>
+          <t>'-7.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>126</v>
       </c>
       <c r="F19" t="n">
-        <v>549</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>1647</v>
+        <v>462</v>
       </c>
       <c r="H19" t="n">
-        <v>46.3</v>
+        <v>3.43</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>250500</v>
+        <v>15720</v>
       </c>
       <c r="K19" t="n">
-        <v>241500</v>
+        <v>14770</v>
       </c>
       <c r="L19" t="n">
-        <v>244000</v>
+        <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>228000</v>
+        <v>14160</v>
       </c>
       <c r="N19" t="n">
-        <v>46.35</v>
+        <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>4647835653500</v>
+        <v>87074820990</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-5208000</v>
+        <v>71000</v>
       </c>
       <c r="S19" t="n">
-        <v>223000</v>
+        <v>-9000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 논쟁이 주를 이루며, 주가 하락에 대한 정치적 책임론 제기. 기술 유출 관련 언급.</t>
+          <t>3분기 어닝 서프라이즈(매출 668억, 영업이익 59억) 등 실적 호조 및 외인 대량 매수가 언급됨. 하지만 미국 업체와의 기술력 차이 및 AI 거품론으로 인한 하락 우려도 공존하며, 추세 하락 및 바닥을 7000원으로 예상하는 의견도 있음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['정치', '주가 하락', '기술 유출']</t>
+          <t>['어닝 서프라이즈', '외인 매수', 'AI 거품론']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12280</v>
+        <v>231000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.36%</t>
+          <t>'-7.78%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>188</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>105</v>
+        <v>547</v>
       </c>
       <c r="G20" t="n">
-        <v>448</v>
+        <v>1695</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>46.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13400</v>
+        <v>250500</v>
       </c>
       <c r="K20" t="n">
-        <v>13750</v>
+        <v>241500</v>
       </c>
       <c r="L20" t="n">
-        <v>15390</v>
+        <v>244000</v>
       </c>
       <c r="M20" t="n">
-        <v>11980</v>
+        <v>228000</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>46.35</v>
       </c>
       <c r="O20" t="n">
-        <v>197075600870</v>
+        <v>4750906596000</v>
       </c>
       <c r="P20" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>3200</v>
+        <v>90200</v>
       </c>
       <c r="R20" t="n">
-        <v>-22000</v>
+        <v>-5208000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>223000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주포의 움직임과 공매도 관련 언급. 반도체 호남 클러스터 관련 내용 혼재.</t>
+          <t>현 정부 정책 및 정치적 이슈에 대한 비판이 주를 이루며, 삼성전자 주가 하락의 원인으로 정치 상황을 지목함. 일부에서는 기술 유출 관련 처벌 강화 및 외인 매수 촉구를 주장함.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주포', '공매도', '반도체 클러스터']</t>
+          <t>['정치적 이슈', '기술 유출', '외인 매수']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18650</v>
+        <v>18700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.80%</t>
+          <t>'-8.56%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G21" t="n">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="H21" t="n">
         <v>0.73</v>
@@ -2358,7 +2358,7 @@
         <v>0.34</v>
       </c>
       <c r="O21" t="n">
-        <v>97369996335</v>
+        <v>98893573505</v>
       </c>
       <c r="P21" t="n">
         <v>62100</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>보호예수 물량 및 외부 조달 판매 의혹 제기. 단기 급등락 반복 및 주가 조작 의심, 투자자들의 혼란과 불신 심화.</t>
+          <t>주가 조작 및 도박장 의혹 제기. 자체 로봇 기술 부족 및 물량 떠넘기기 의심. 보호예수 관련 논란.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보호예수', '주가 조작', '단기 급등락']</t>
+          <t>['주가 조작', '보호예수', '로봇 기술']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1447000</v>
+        <v>12160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.84%</t>
+          <t>'-9.25%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>-1.01</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>191</v>
       </c>
       <c r="F22" t="n">
-        <v>586</v>
+        <v>107</v>
       </c>
       <c r="G22" t="n">
-        <v>1360</v>
+        <v>453</v>
       </c>
       <c r="H22" t="n">
-        <v>49.41</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1605000</v>
+        <v>13400</v>
       </c>
       <c r="K22" t="n">
-        <v>1538000</v>
+        <v>13750</v>
       </c>
       <c r="L22" t="n">
-        <v>1554000</v>
+        <v>15390</v>
       </c>
       <c r="M22" t="n">
-        <v>1431000</v>
+        <v>11980</v>
       </c>
       <c r="N22" t="n">
-        <v>49.52</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
-        <v>6264893914000</v>
+        <v>197875351460</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>19380</v>
       </c>
       <c r="Q22" t="n">
-        <v>403000</v>
+        <v>3200</v>
       </c>
       <c r="R22" t="n">
-        <v>-1301000</v>
+        <v>-22000</v>
       </c>
       <c r="S22" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 호남 투자 관련 부정적 언급이 주를 이룸. 최태원 관련 비판.</t>
+          <t>주포의 움직임과 공매도 관련 언급. 반도체 호남 클러스터 관련 내용 혼재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['정치', '호남 투자', '최태원']</t>
+          <t>['주포', '공매도', '반도체 클러스터']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6660</v>
+        <v>1447000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.12%</t>
+          <t>'-9.84%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>159</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>69</v>
+        <v>580</v>
       </c>
       <c r="G23" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8</v>
+        <v>49.41</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7410</v>
+        <v>1605000</v>
       </c>
       <c r="K23" t="n">
-        <v>7330</v>
+        <v>1538000</v>
       </c>
       <c r="L23" t="n">
-        <v>8040</v>
+        <v>1554000</v>
       </c>
       <c r="M23" t="n">
-        <v>6600</v>
+        <v>1431000</v>
       </c>
       <c r="N23" t="n">
-        <v>1.99</v>
+        <v>49.52</v>
       </c>
       <c r="O23" t="n">
-        <v>70543004105</v>
+        <v>6401456086500</v>
       </c>
       <c r="P23" t="n">
-        <v>23500</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>2890</v>
+        <v>403000</v>
       </c>
       <c r="R23" t="n">
-        <v>-277000</v>
+        <v>-1301000</v>
       </c>
       <c r="S23" t="n">
-        <v>-218000</v>
+        <v>114000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>수도권 거점 공장 보유 및 건설 기초 소재 대장주 명성에도 불구하고, 개인 투자자 매도 및 대차 거래 증가 우려. 주포 움직임에 대한 논란.</t>
+          <t>정부 정책 및 지역 투자(호남 반도체 클러스터)에 대한 불만이 제기되며, 주가 하락의 원인으로 지목됨. 최태원 회장에 대한 비판과 솔다임 상장 관련 의혹도 제기됨.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,18 +2567,110 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['건설 기초 소재', '주포', '대차 거래']</t>
+          <t>['정부 정책', '호남 투자', '솔다임']</t>
         </is>
       </c>
       <c r="X23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>삼표시멘트</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6630</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>'-10.53%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E24" t="n">
+        <v>164</v>
+      </c>
+      <c r="F24" t="n">
+        <v>71</v>
+      </c>
+      <c r="G24" t="n">
+        <v>405</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>7410</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7330</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8040</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6600</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O24" t="n">
+        <v>71032516750</v>
+      </c>
+      <c r="P24" t="n">
+        <v>23500</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2890</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-277000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-218000</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>건설기초소재 대장주로 언급되며 수도권 거점 공장 및 점유율 관련 내용이 있으나, 차트 분석과 더불어 매도 완료 및 밑에서 다시 보자는 의견이 일부 있음. 주포에 대한 부정적인 언급도 존재함.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['건설기초소재', '수도권 공장', '주포']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
         <v>4</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>038500</t>
         </is>
